--- a/backend/src/workflows/claim-status/portals/availity/config/Provider_mapping_ava.xlsx
+++ b/backend/src/workflows/claim-status/portals/availity/config/Provider_mapping_ava.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alamelu\Documents\Repos\claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F166DB-17F9-4065-B5C4-45D7F0CB0CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB91FC84-B1A7-4C71-A036-841CB06F4E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{23A9B4C9-241C-49FD-8075-596679F43269}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>Project</t>
   </si>
@@ -49,6 +49,12 @@
   </si>
   <si>
     <t>INLAND EAR NOSE AND THROAT A MEDICAL GROUP INC</t>
+  </si>
+  <si>
+    <t>ABID HAMEED KHAN MD PROFESSIONAL CORPORATION</t>
+  </si>
+  <si>
+    <t>AHK</t>
   </si>
 </sst>
 </file>
@@ -64,12 +70,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -84,8 +96,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,23 +413,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B069185-49CE-47C1-9999-4059920B3B1C}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="23.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="45.7109375" customWidth="1"/>
+    <col min="3" max="3" width="53.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -431,6 +444,20 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>6</v>
       </c>
     </row>

--- a/backend/src/workflows/claim-status/portals/availity/config/Provider_mapping_ava.xlsx
+++ b/backend/src/workflows/claim-status/portals/availity/config/Provider_mapping_ava.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alamelu\Documents\Repos\claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB91FC84-B1A7-4C71-A036-841CB06F4E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA6B24D-B297-4BB7-BD55-FB3DD48F11CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{23A9B4C9-241C-49FD-8075-596679F43269}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>Project</t>
   </si>
@@ -55,6 +55,36 @@
   </si>
   <si>
     <t>AHK</t>
+  </si>
+  <si>
+    <t>IUMG</t>
+  </si>
+  <si>
+    <t>INLAND UROLOGY MEDICAL GROUP</t>
+  </si>
+  <si>
+    <t>ELITE MEDICAL GROUP OF SOUTHERN CALIFORNIA</t>
+  </si>
+  <si>
+    <t>ESC</t>
+  </si>
+  <si>
+    <t>MMG</t>
+  </si>
+  <si>
+    <t>Medicor Medical Group</t>
+  </si>
+  <si>
+    <t>TAJ</t>
+  </si>
+  <si>
+    <t>JAMIL, TARIQ</t>
+  </si>
+  <si>
+    <t>Nurick Harvey</t>
+  </si>
+  <si>
+    <t>NUR</t>
   </si>
 </sst>
 </file>
@@ -413,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B069185-49CE-47C1-9999-4059920B3B1C}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="23.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="53.140625" customWidth="1"/>
@@ -461,6 +491,76 @@
         <v>6</v>
       </c>
     </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend/src/workflows/claim-status/portals/availity/config/Provider_mapping_ava.xlsx
+++ b/backend/src/workflows/claim-status/portals/availity/config/Provider_mapping_ava.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alamelu\Documents\Repos\claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vignesh\Desktop\Vignesh\claim-status\iehp-claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA6B24D-B297-4BB7-BD55-FB3DD48F11CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A971358-C7B7-4558-BCE8-2517EA4EBE7A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{23A9B4C9-241C-49FD-8075-596679F43269}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>Project</t>
   </si>
@@ -85,6 +85,15 @@
   </si>
   <si>
     <t>NUR</t>
+  </si>
+  <si>
+    <t>Charm</t>
+  </si>
+  <si>
+    <t>open mind</t>
+  </si>
+  <si>
+    <t>OPEN MIND MENTAL HEALTH PHYSICIANS, INC.</t>
   </si>
 </sst>
 </file>
@@ -443,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B069185-49CE-47C1-9999-4059920B3B1C}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="23.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="53.140625" customWidth="1"/>
@@ -561,6 +570,20 @@
         <v>6</v>
       </c>
     </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend/src/workflows/claim-status/portals/availity/config/Provider_mapping_ava.xlsx
+++ b/backend/src/workflows/claim-status/portals/availity/config/Provider_mapping_ava.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alamelu\Documents\Repos\claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA6B24D-B297-4BB7-BD55-FB3DD48F11CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81890FA-52B6-41C4-A451-1DD9985659D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{23A9B4C9-241C-49FD-8075-596679F43269}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="34">
   <si>
     <t>Project</t>
   </si>
@@ -85,6 +85,48 @@
   </si>
   <si>
     <t>NUR</t>
+  </si>
+  <si>
+    <t>San Antonio Regional Medical Group Inc</t>
+  </si>
+  <si>
+    <t>BASIM Z. ABDELKARIM, M.D., INC.</t>
+  </si>
+  <si>
+    <t>SARMG</t>
+  </si>
+  <si>
+    <t>BZA</t>
+  </si>
+  <si>
+    <t>S.M. HAMMAD RIZVI, M.D. INC</t>
+  </si>
+  <si>
+    <t>SMHR</t>
+  </si>
+  <si>
+    <t>TAT</t>
+  </si>
+  <si>
+    <t>TIFFANY ANDERSON TERRELL DO INC</t>
+  </si>
+  <si>
+    <t>BPH</t>
+  </si>
+  <si>
+    <t>TWL</t>
+  </si>
+  <si>
+    <t>WMGU</t>
+  </si>
+  <si>
+    <t>HIRSCH, BRANDON</t>
+  </si>
+  <si>
+    <t>THOMAS W LEE MD INC</t>
+  </si>
+  <si>
+    <t>WOMEN'S MEDICAL GROUP OF UPLAND INC.</t>
   </si>
 </sst>
 </file>
@@ -443,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B069185-49CE-47C1-9999-4059920B3B1C}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="23.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="53.140625" customWidth="1"/>
@@ -561,6 +603,104 @@
         <v>6</v>
       </c>
     </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend/src/workflows/claim-status/portals/availity/config/Provider_mapping_ava.xlsx
+++ b/backend/src/workflows/claim-status/portals/availity/config/Provider_mapping_ava.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vignesh\Desktop\Vignesh\claim-status\iehp-claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hayagriva\Documents\Github Pages\iehp-claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A971358-C7B7-4558-BCE8-2517EA4EBE7A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57974ABA-DB86-4387-B477-6CA546FAE7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{23A9B4C9-241C-49FD-8075-596679F43269}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{23A9B4C9-241C-49FD-8075-596679F43269}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -90,10 +90,10 @@
     <t>Charm</t>
   </si>
   <si>
-    <t>open mind</t>
-  </si>
-  <si>
     <t>OPEN MIND MENTAL HEALTH PHYSICIANS, INC.</t>
+  </si>
+  <si>
+    <t>Open Mind</t>
   </si>
 </sst>
 </file>
@@ -453,12 +453,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B069185-49CE-47C1-9999-4059920B3B1C}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="23.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="53.140625" customWidth="1"/>
+    <col min="3" max="3" width="53.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -472,7 +472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -486,7 +486,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -500,7 +500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -514,7 +514,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -528,7 +528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -542,7 +542,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -556,7 +556,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -570,15 +570,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>20</v>
       </c>
       <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
       </c>
       <c r="D9" t="s">
         <v>6</v>

--- a/backend/src/workflows/claim-status/portals/availity/config/Provider_mapping_ava.xlsx
+++ b/backend/src/workflows/claim-status/portals/availity/config/Provider_mapping_ava.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alamelu\Documents\Repos\claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81890FA-52B6-41C4-A451-1DD9985659D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D843440-64B8-4F49-A61F-0FA4D13BE21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{23A9B4C9-241C-49FD-8075-596679F43269}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="48">
   <si>
     <t>Project</t>
   </si>
@@ -127,6 +127,48 @@
   </si>
   <si>
     <t>WOMEN'S MEDICAL GROUP OF UPLAND INC.</t>
+  </si>
+  <si>
+    <t>CTH</t>
+  </si>
+  <si>
+    <t>HUNG, CHUANG TI</t>
+  </si>
+  <si>
+    <t>Jenkins, Kevin Michael</t>
+  </si>
+  <si>
+    <t>KMJ</t>
+  </si>
+  <si>
+    <t>CHIRIANO, JASON TODD</t>
+  </si>
+  <si>
+    <t>JTC</t>
+  </si>
+  <si>
+    <t>MAIN</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>UPLAND SURGICAL ASSOCIATES</t>
+  </si>
+  <si>
+    <t>NEPHROLOGY ASSOCIATES OF UPLAND AND POMONA</t>
+  </si>
+  <si>
+    <t>GHASSAN HADI MD INC</t>
+  </si>
+  <si>
+    <t>GEH</t>
+  </si>
+  <si>
+    <t>ALPINER, DONALD MARK</t>
+  </si>
+  <si>
+    <t>DMA</t>
   </si>
 </sst>
 </file>
@@ -485,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B069185-49CE-47C1-9999-4059920B3B1C}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultColWidth="23.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="53.140625" customWidth="1"/>
@@ -701,6 +743,104 @@
         <v>6</v>
       </c>
     </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
